--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_9_12.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_9_12.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63392.521719796</v>
+        <v>56618.71411520857</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9858951.653791893</v>
+        <v>10137812.57763006</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22081763.57343303</v>
+        <v>22039391.87547411</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4145624.528972384</v>
+        <v>4145497.772990323</v>
       </c>
     </row>
     <row r="11">
@@ -8433,25 +8433,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>213.4420168741263</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L8" t="n">
-        <v>227.519188839334</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M8" t="n">
-        <v>221.1696050865692</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N8" t="n">
-        <v>220.0879480187015</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O8" t="n">
-        <v>221.2927692106315</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P8" t="n">
-        <v>223.7177545492394</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q8" t="n">
-        <v>212.3149906599047</v>
+        <v>207.1020630664798</v>
       </c>
       <c r="R8" t="n">
         <v>65.71641987298243</v>
@@ -8509,28 +8509,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J9" t="n">
-        <v>124.1958059119497</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K9" t="n">
-        <v>133.3261465215288</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L9" t="n">
-        <v>132.4830118553459</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M9" t="n">
-        <v>135.0490339220183</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N9" t="n">
-        <v>124.0691932154088</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O9" t="n">
-        <v>135.9433104821803</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P9" t="n">
-        <v>128.6348413765944</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q9" t="n">
-        <v>136.4124155954555</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,19 +8594,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>131.3993975927137</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M10" t="n">
-        <v>135.251046242687</v>
+        <v>129.0262495446562</v>
       </c>
       <c r="N10" t="n">
-        <v>124.0981838094955</v>
+        <v>118.0213988638391</v>
       </c>
       <c r="O10" t="n">
-        <v>135.1430302551215</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P10" t="n">
-        <v>134.892725360623</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q10" t="n">
         <v>65.34295837775146</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K11" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L11" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M11" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N11" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O11" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P11" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q11" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,13 +8746,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K12" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L12" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -8764,10 +8764,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q12" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L13" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M13" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N13" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O13" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P13" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K14" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L14" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M14" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N14" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O14" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P14" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q14" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,13 +8983,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K15" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L15" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -9001,10 +9001,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q15" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L16" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M16" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N16" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O16" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P16" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K17" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L17" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M17" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N17" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O17" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P17" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,13 +9220,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K18" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L18" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q18" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L19" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M19" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N19" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O19" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P19" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K20" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L20" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M20" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N20" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O20" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P20" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q20" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,13 +9457,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K21" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L21" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9475,10 +9475,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q21" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L22" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M22" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N22" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O22" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P22" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K23" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L23" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M23" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N23" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O23" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P23" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q23" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,13 +9694,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K24" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L24" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q24" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L25" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M25" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N25" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O25" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P25" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K26" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L26" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M26" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N26" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O26" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P26" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q26" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,13 +9931,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K27" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L27" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9949,10 +9949,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q27" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L28" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M28" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N28" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O28" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P28" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K29" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L29" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M29" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N29" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O29" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P29" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q29" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,13 +10168,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K30" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L30" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -10186,10 +10186,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q30" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L31" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M31" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N31" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O31" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P31" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K32" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L32" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M32" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N32" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O32" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P32" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q32" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,13 +10405,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K33" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L33" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -10423,10 +10423,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q33" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L34" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M34" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N34" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O34" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P34" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K35" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L35" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M35" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N35" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O35" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P35" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q35" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,13 +10642,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K36" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L36" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -10660,10 +10660,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q36" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L37" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M37" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N37" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O37" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P37" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K38" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L38" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M38" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N38" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O38" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P38" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q38" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,13 +10879,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K39" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L39" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -10897,10 +10897,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q39" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L40" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M40" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N40" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O40" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P40" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K41" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L41" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M41" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N41" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O41" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P41" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q41" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,13 +11116,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K42" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L42" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -11134,10 +11134,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q42" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L43" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M43" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N43" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O43" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P43" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>85.85082412467622</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K44" t="n">
-        <v>77.41710230126196</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L44" t="n">
-        <v>58.76825416596711</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M44" t="n">
-        <v>33.40167543832803</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N44" t="n">
-        <v>29.28173696342509</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O44" t="n">
-        <v>41.11987473826963</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P44" t="n">
-        <v>69.94435756431477</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q44" t="n">
-        <v>101.1846396231932</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,13 +11353,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>70.14008893081763</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K45" t="n">
-        <v>40.93631633284956</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L45" t="n">
-        <v>8.253483553459063</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -11371,10 +11371,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>19.37910552753777</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q45" t="n">
-        <v>63.37784955771961</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>70.56047128528949</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L46" t="n">
-        <v>60.08523365828746</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M46" t="n">
-        <v>60.06025935744114</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N46" t="n">
-        <v>50.69526577670855</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O46" t="n">
-        <v>67.3435548452854</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P46" t="n">
-        <v>76.87856142619682</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22993,16 +22993,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>415.2504762086024</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H8" t="n">
-        <v>338.9395810102395</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I8" t="n">
-        <v>208.4610855503054</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J8" t="n">
-        <v>7.513676289285883</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,19 +23023,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.347066048715659</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>146.5862586446673</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S8" t="n">
-        <v>207.8291650636323</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T8" t="n">
-        <v>222.8670756947846</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3414720033139</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,13 +23072,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3155548990597</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H9" t="n">
-        <v>111.9653876327229</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I9" t="n">
-        <v>88.43389700235848</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23105,16 +23105,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>98.42172094509596</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S9" t="n">
-        <v>171.163784311385</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T9" t="n">
-        <v>200.0520211476518</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9395424583333</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9675367355079</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H10" t="n">
-        <v>162.0187462779314</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I10" t="n">
-        <v>154.7454913207009</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J10" t="n">
-        <v>91.70178667404983</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K10" t="n">
-        <v>19.5458852685058</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23181,19 +23181,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>84.19904325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R10" t="n">
-        <v>176.239325803399</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S10" t="n">
-        <v>223.6080570533657</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T10" t="n">
-        <v>227.8454254938553</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U10" t="n">
-        <v>286.3177506679663</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H11" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I11" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S11" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T11" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H12" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I12" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S12" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T12" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H13" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I13" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J13" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R13" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S13" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T13" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U13" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H14" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I14" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S14" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T14" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H15" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I15" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S15" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T15" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H16" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I16" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J16" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R16" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S16" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T16" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U16" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H17" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I17" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S17" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T17" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H18" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I18" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S18" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T18" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H19" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I19" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J19" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R19" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S19" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T19" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U19" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H20" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I20" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S20" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T20" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H21" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I21" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S21" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T21" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H22" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I22" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J22" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R22" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S22" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T22" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U22" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H23" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I23" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S23" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T23" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H24" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I24" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S24" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T24" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H25" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I25" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J25" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R25" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S25" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T25" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U25" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H26" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I26" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S26" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T26" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H27" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I27" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S27" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T27" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H28" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I28" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J28" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R28" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S28" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T28" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U28" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H29" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I29" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S29" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T29" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H30" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I30" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S30" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T30" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H31" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I31" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J31" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R31" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S31" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T31" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U31" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H32" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I32" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S32" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T32" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H33" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I33" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S33" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T33" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H34" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I34" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J34" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R34" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S34" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T34" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U34" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H35" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I35" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S35" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T35" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H36" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I36" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S36" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T36" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H37" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I37" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J37" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R37" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S37" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T37" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U37" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H38" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I38" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S38" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T38" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H39" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I39" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S39" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T39" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H40" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I40" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J40" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R40" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S40" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T40" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U40" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H41" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I41" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S41" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T41" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H42" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I42" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S42" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T42" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H43" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I43" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J43" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R43" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S43" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T43" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U43" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.181129474934</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H44" t="n">
-        <v>327.9881337740586</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I44" t="n">
-        <v>167.2350956005567</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>79.41390688587329</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S44" t="n">
-        <v>183.4614263701649</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T44" t="n">
-        <v>218.1860103681515</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2559242646204</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.7434039556635</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H45" t="n">
-        <v>106.4396140478172</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I45" t="n">
-        <v>68.73484039858488</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>62.89817377528463</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S45" t="n">
-        <v>160.5363314811963</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T45" t="n">
-        <v>197.745851336331</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9019009488993</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4878646043604</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H46" t="n">
-        <v>157.754024966456</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I46" t="n">
-        <v>140.320442140373</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J46" t="n">
-        <v>57.78896700191869</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>44.03304325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R46" t="n">
-        <v>154.6715225247105</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S46" t="n">
-        <v>215.2486800041854</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T46" t="n">
-        <v>225.7959172971339</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U46" t="n">
-        <v>286.29158673354</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>361456.8995456908</v>
+        <v>362700.8593270332</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>357840.2091359296</v>
+        <v>357693.0542933804</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64504.44331886783</v>
+        <v>64504.44331886782</v>
       </c>
       <c r="C2" t="n">
         <v>64504.44331886782</v>
       </c>
       <c r="D2" t="n">
-        <v>65058.63286563388</v>
+        <v>65823.63520640059</v>
       </c>
       <c r="E2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="F2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="G2" t="n">
-        <v>70900.7346728281</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="H2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="I2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="J2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="K2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="L2" t="n">
-        <v>70900.73467282813</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="M2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="N2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="O2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
       <c r="P2" t="n">
-        <v>70900.73467282811</v>
+        <v>71260.70145735363</v>
       </c>
     </row>
     <row r="3">
@@ -26319,10 +26319,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>11133.382</v>
+        <v>29992.69797750899</v>
       </c>
       <c r="E3" t="n">
-        <v>213705.198</v>
+        <v>210211.2631018186</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48378.33248915087</v>
+        <v>49934.7668093977</v>
       </c>
       <c r="C4" t="n">
-        <v>48378.33248915088</v>
+        <v>49934.7668093977</v>
       </c>
       <c r="D4" t="n">
-        <v>47006.84069512705</v>
+        <v>45986.66366669783</v>
       </c>
       <c r="E4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="F4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="G4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="H4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="I4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="J4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="K4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="L4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="M4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="N4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="O4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
       <c r="P4" t="n">
-        <v>15153.32488392675</v>
+        <v>13693.13678223465</v>
       </c>
     </row>
     <row r="5">
@@ -26423,43 +26423,43 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>33911</v>
+        <v>34391.06348367693</v>
       </c>
       <c r="E5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="F5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="G5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="H5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="I5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="J5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="K5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="L5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="M5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="N5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="O5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="P5" t="n">
-        <v>6082.2</v>
+        <v>6467.457040608691</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-17501.48917028304</v>
+        <v>-19057.92349052988</v>
       </c>
       <c r="C6" t="n">
-        <v>-17501.48917028306</v>
+        <v>-19057.92349052988</v>
       </c>
       <c r="D6" t="n">
-        <v>-26992.58982949317</v>
+        <v>-44546.78992148316</v>
       </c>
       <c r="E6" t="n">
-        <v>-164039.9882110987</v>
+        <v>-159111.1554673083</v>
       </c>
       <c r="F6" t="n">
-        <v>49665.20978890137</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="G6" t="n">
-        <v>49665.20978890135</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="H6" t="n">
-        <v>49665.20978890137</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="I6" t="n">
-        <v>49665.20978890137</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="J6" t="n">
-        <v>49665.20978890137</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="K6" t="n">
-        <v>49665.20978890137</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="L6" t="n">
-        <v>49665.20978890138</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="M6" t="n">
-        <v>49665.20978890137</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="N6" t="n">
-        <v>49665.20978890137</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="O6" t="n">
-        <v>49665.20978890137</v>
+        <v>51100.10763451028</v>
       </c>
       <c r="P6" t="n">
-        <v>49665.20978890137</v>
+        <v>51100.10763451028</v>
       </c>
     </row>
   </sheetData>
@@ -26681,43 +26681,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>35.02126071912533</v>
       </c>
       <c r="E3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="F3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="G3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="H3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="I3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="J3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="K3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="L3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="M3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="N3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="O3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>296.6723413123253</v>
       </c>
     </row>
     <row r="4">
@@ -26898,10 +26898,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="E3" t="n">
-        <v>266</v>
+        <v>261.6510805931999</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05226130653266328</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5352211055276379</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I8" t="n">
-        <v>2.014804020100503</v>
+        <v>5.427767452760119</v>
       </c>
       <c r="J8" t="n">
-        <v>4.435613065326634</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
-        <v>6.647834170854272</v>
+        <v>17.90888720884599</v>
       </c>
       <c r="L8" t="n">
-        <v>8.247226130653267</v>
+        <v>22.21755819470702</v>
       </c>
       <c r="M8" t="n">
-        <v>9.176628140703517</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N8" t="n">
-        <v>9.325115577889449</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O8" t="n">
-        <v>8.805442211055276</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P8" t="n">
-        <v>7.515241206030151</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.643633165829145</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R8" t="n">
-        <v>3.282859296482413</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S8" t="n">
-        <v>1.190904522613066</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2287738693467336</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004180904522613061</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0279622641509434</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H9" t="n">
-        <v>0.270056603773585</v>
+        <v>0.7275171330520187</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9627358490566039</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J9" t="n">
-        <v>2.641820754716981</v>
+        <v>7.116914878779989</v>
       </c>
       <c r="K9" t="n">
-        <v>4.515292452830189</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L9" t="n">
-        <v>6.071367924528302</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M9" t="n">
-        <v>7.084999999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N9" t="n">
-        <v>7.272518867924529</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O9" t="n">
-        <v>6.652933962264151</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P9" t="n">
-        <v>5.33956603773585</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.569358490566038</v>
+        <v>9.615648792164375</v>
       </c>
       <c r="R9" t="n">
-        <v>1.736113207547171</v>
+        <v>4.676990252263569</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5193867924528298</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1127075471698113</v>
+        <v>0.3036277226497752</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001839622641509435</v>
+        <v>0.004955838781008304</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02344262295081967</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2084262295081968</v>
+        <v>0.5614884095623703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7049836065573772</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J10" t="n">
-        <v>1.657393442622951</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K10" t="n">
-        <v>2.723606557377048</v>
+        <v>7.337241180170845</v>
       </c>
       <c r="L10" t="n">
-        <v>3.48527868852459</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M10" t="n">
-        <v>3.674737704918032</v>
+        <v>9.899534402948818</v>
       </c>
       <c r="N10" t="n">
-        <v>3.587360655737707</v>
+        <v>9.664145601394049</v>
       </c>
       <c r="O10" t="n">
-        <v>3.313508196721312</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P10" t="n">
-        <v>2.835278688524589</v>
+        <v>7.638079550938412</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.963</v>
+        <v>5.288210368587925</v>
       </c>
       <c r="R10" t="n">
-        <v>1.054065573770491</v>
+        <v>2.839592713390063</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4085409836065572</v>
+        <v>1.100586177025627</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1001639344262295</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001278688524590165</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H11" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I11" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J11" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K11" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L11" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M11" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N11" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O11" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P11" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q11" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R11" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S11" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T11" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,22 +31749,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H12" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I12" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J12" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K12" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L12" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
@@ -31776,22 +31776,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q12" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R12" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S12" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T12" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H13" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I13" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J13" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K13" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L13" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M13" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N13" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O13" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P13" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R13" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S13" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T13" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H14" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I14" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J14" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K14" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L14" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M14" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N14" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O14" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P14" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q14" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R14" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S14" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T14" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,22 +31986,22 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H15" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I15" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J15" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K15" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L15" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
         <v>142.1340339220183</v>
@@ -32013,22 +32013,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q15" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R15" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S15" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T15" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H16" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I16" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J16" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K16" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L16" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M16" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N16" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O16" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P16" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R16" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S16" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H17" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I17" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J17" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K17" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L17" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M17" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N17" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O17" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P17" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q17" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R17" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S17" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T17" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,22 +32223,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H18" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I18" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J18" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K18" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L18" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -32250,22 +32250,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q18" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R18" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S18" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T18" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H19" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I19" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J19" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K19" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L19" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M19" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N19" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O19" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P19" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q19" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R19" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S19" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H20" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I20" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J20" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K20" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L20" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M20" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N20" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O20" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P20" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q20" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R20" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S20" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T20" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,22 +32460,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H21" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I21" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J21" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K21" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L21" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
@@ -32487,22 +32487,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q21" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R21" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S21" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T21" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H22" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I22" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J22" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K22" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L22" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M22" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N22" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O22" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P22" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q22" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R22" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S22" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T22" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H23" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I23" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J23" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K23" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L23" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M23" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N23" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O23" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P23" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q23" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R23" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S23" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T23" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,22 +32697,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H24" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I24" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J24" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K24" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L24" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
@@ -32724,22 +32724,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q24" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R24" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S24" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T24" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H25" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I25" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J25" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K25" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L25" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M25" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N25" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O25" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P25" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q25" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R25" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S25" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T25" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H26" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I26" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J26" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K26" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L26" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M26" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N26" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O26" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P26" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q26" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R26" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S26" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T26" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U26" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,22 +32934,22 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H27" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I27" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J27" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K27" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L27" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -32961,22 +32961,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q27" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R27" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S27" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T27" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U27" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H28" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I28" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J28" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K28" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L28" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M28" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N28" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O28" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P28" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q28" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R28" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S28" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T28" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H29" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I29" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J29" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K29" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L29" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M29" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N29" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O29" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P29" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q29" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R29" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S29" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T29" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U29" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,22 +33171,22 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H30" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I30" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J30" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K30" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L30" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
         <v>142.1340339220183</v>
@@ -33198,22 +33198,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q30" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R30" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S30" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T30" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U30" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H31" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I31" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J31" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K31" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L31" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M31" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N31" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O31" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P31" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q31" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R31" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S31" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T31" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H32" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I32" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J32" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K32" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L32" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M32" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N32" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O32" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P32" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q32" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R32" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S32" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T32" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U32" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,22 +33408,22 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H33" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I33" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J33" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K33" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L33" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
         <v>142.1340339220183</v>
@@ -33435,22 +33435,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q33" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R33" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S33" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T33" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U33" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H34" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I34" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J34" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K34" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L34" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M34" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N34" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O34" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P34" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q34" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R34" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S34" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T34" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U34" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H35" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I35" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J35" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K35" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L35" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M35" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N35" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O35" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P35" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q35" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R35" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S35" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T35" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,22 +33645,22 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H36" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I36" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J36" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K36" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L36" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
         <v>142.1340339220183</v>
@@ -33672,22 +33672,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q36" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R36" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S36" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T36" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U36" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H37" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I37" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J37" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K37" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L37" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M37" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N37" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O37" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P37" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q37" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R37" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S37" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T37" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U37" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H38" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I38" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J38" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K38" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L38" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M38" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N38" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O38" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P38" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q38" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R38" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S38" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T38" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,22 +33882,22 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H39" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I39" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J39" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K39" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L39" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
         <v>142.1340339220183</v>
@@ -33909,22 +33909,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q39" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R39" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S39" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T39" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H40" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I40" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J40" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K40" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L40" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M40" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N40" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O40" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P40" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q40" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R40" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S40" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T40" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U40" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H41" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I41" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J41" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K41" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L41" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M41" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N41" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O41" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P41" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q41" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R41" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S41" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T41" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U41" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,22 +34119,22 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H42" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I42" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J42" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K42" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L42" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
@@ -34146,22 +34146,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q42" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R42" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S42" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T42" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U42" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H43" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I43" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J43" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K43" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L43" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M43" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N43" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O43" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P43" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q43" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R43" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S43" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T43" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U43" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.121608040201004</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H44" t="n">
-        <v>11.48666834170854</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I44" t="n">
-        <v>43.24079396984926</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J44" t="n">
-        <v>95.19508040201006</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K44" t="n">
-        <v>142.6727487437186</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L44" t="n">
-        <v>176.9981608040201</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M44" t="n">
-        <v>196.9445577889447</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N44" t="n">
-        <v>200.1313266331658</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O44" t="n">
-        <v>188.9783366834171</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P44" t="n">
-        <v>161.2886381909548</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q44" t="n">
-        <v>121.1210502512563</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R44" t="n">
-        <v>70.45521105527639</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S44" t="n">
-        <v>25.55864321608041</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T44" t="n">
-        <v>4.909839195979898</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08972864321608032</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,22 +34356,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6001132075471698</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H45" t="n">
-        <v>5.795830188679246</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I45" t="n">
-        <v>20.66179245283019</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J45" t="n">
-        <v>56.69753773584907</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K45" t="n">
-        <v>96.90512264150944</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L45" t="n">
-        <v>130.3008962264151</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
         <v>142.1340339220183</v>
@@ -34383,22 +34383,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>114.5953018867925</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q45" t="n">
-        <v>76.6039245283019</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R45" t="n">
-        <v>37.25966037735851</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S45" t="n">
-        <v>11.1468396226415</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T45" t="n">
-        <v>2.418877358490565</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U45" t="n">
-        <v>0.03948113207547171</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5031147540983606</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H46" t="n">
-        <v>4.473147540983609</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I46" t="n">
-        <v>15.13003278688525</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J46" t="n">
-        <v>35.57021311475409</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K46" t="n">
-        <v>58.45278688524589</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L46" t="n">
-        <v>74.79944262295082</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M46" t="n">
-        <v>78.86552459016391</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N46" t="n">
-        <v>76.99027868852464</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O46" t="n">
-        <v>71.11298360655739</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P46" t="n">
-        <v>60.84944262295079</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q46" t="n">
-        <v>42.129</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R46" t="n">
-        <v>22.62186885245901</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S46" t="n">
-        <v>8.767918032786881</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T46" t="n">
-        <v>2.14967213114754</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U46" t="n">
-        <v>0.0274426229508197</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
